--- a/Capstone_Project/09_Project_Management_Evidence/Group-3_Risk_Issue_Change_Register.xlsx
+++ b/Capstone_Project/09_Project_Management_Evidence/Group-3_Risk_Issue_Change_Register.xlsx
@@ -17,9 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="dd mmm yyyy"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd mmm yyyy"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -89,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -99,7 +98,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -561,7 +563,7 @@
           <t>Risk</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>46314</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -599,10 +601,14 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="K4" s="6" t="n">
         <v>46324</v>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Eight of eight coding tasks merged on 22 October and testing fixes are retested</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -615,7 +621,7 @@
           <t>Risk</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>46314</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -653,7 +659,7 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="K5" s="6" t="n">
         <v>46324</v>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
@@ -669,7 +675,7 @@
           <t>Risk</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>46314</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -707,7 +713,7 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="K6" s="5" t="n">
+      <c r="K6" s="6" t="n">
         <v>46324</v>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -723,7 +729,7 @@
           <t>Risk</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>46314</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -758,15 +764,15 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="n">
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="n">
         <v>46324</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Survey being shared with students</t>
+          <t>13 students answered the survey on 22 October so the target of 10 was met and user testing numbers are still to be confirmed</t>
         </is>
       </c>
     </row>
@@ -781,7 +787,7 @@
           <t>Risk</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>46314</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -819,7 +825,7 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="K8" s="5" t="n">
+      <c r="K8" s="6" t="n">
         <v>46324</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -839,7 +845,7 @@
           <t>Risk</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>46314</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -877,7 +883,7 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="K9" s="6" t="n">
         <v>46324</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -897,7 +903,7 @@
           <t>Issue</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>46311</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -927,7 +933,7 @@
           <t>Resolved</t>
         </is>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="K10" s="6" t="n">
         <v>46314</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -947,7 +953,7 @@
           <t>Issue</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>46311</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -977,7 +983,7 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="K11" s="5" t="n">
+      <c r="K11" s="6" t="n">
         <v>46318</v>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -993,7 +999,7 @@
           <t>Issue</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <v>46311</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1023,7 +1029,7 @@
           <t>Resolved</t>
         </is>
       </c>
-      <c r="K12" s="5" t="n">
+      <c r="K12" s="6" t="n">
         <v>46314</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1043,7 +1049,7 @@
           <t>Change</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="6" t="n">
         <v>46314</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1073,7 +1079,7 @@
           <t>Resolved</t>
         </is>
       </c>
-      <c r="K13" s="5" t="n">
+      <c r="K13" s="6" t="n">
         <v>46314</v>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
@@ -1089,7 +1095,7 @@
           <t>Change</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="6" t="n">
         <v>46314</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1119,7 +1125,7 @@
           <t>Resolved</t>
         </is>
       </c>
-      <c r="K14" s="5" t="n">
+      <c r="K14" s="6" t="n">
         <v>46314</v>
       </c>
       <c r="L14" s="2" t="inlineStr"/>
@@ -1135,7 +1141,7 @@
           <t>Change</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="6" t="n">
         <v>46314</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1165,7 +1171,7 @@
           <t>Resolved</t>
         </is>
       </c>
-      <c r="K15" s="5" t="n">
+      <c r="K15" s="6" t="n">
         <v>46314</v>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
@@ -1181,7 +1187,7 @@
           <t>Change</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="6" t="n">
         <v>46314</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1211,7 +1217,7 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="K16" s="5" t="n">
+      <c r="K16" s="6" t="n">
         <v>46318</v>
       </c>
       <c r="L16" s="2" t="inlineStr"/>

--- a/Capstone_Project/09_Project_Management_Evidence/Group-3_Risk_Issue_Change_Register.xlsx
+++ b/Capstone_Project/09_Project_Management_Evidence/Group-3_Risk_Issue_Change_Register.xlsx
@@ -764,7 +764,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="K7" s="6" t="n">
@@ -772,7 +772,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13 students answered the survey on 22 October so the target of 10 was met and user testing numbers are still to be confirmed</t>
+          <t>13 students answered the survey on 22 October so the target of 10 was met and user testing will use 5 students and 1 lecturer</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Gerhardus van den Berg</t>
+          <t>Oscar Khumalo</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">

--- a/Capstone_Project/09_Project_Management_Evidence/Group-3_Risk_Issue_Change_Register.xlsx
+++ b/Capstone_Project/09_Project_Management_Evidence/Group-3_Risk_Issue_Change_Register.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="K4" s="6" t="n">
@@ -606,7 +606,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Eight of eight coding tasks merged on 22 October and testing fixes are retested</t>
+          <t>All six must-have features built and all 9 functional requirements met in testing</t>
         </is>
       </c>
     </row>
@@ -656,13 +656,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="K5" s="6" t="n">
         <v>46324</v>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Every member owned tasks, presentation slides and a contribution form</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -710,13 +714,17 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="K6" s="6" t="n">
         <v>46324</v>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>All pages and APIs were built and merged into main</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -772,7 +780,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13 students answered the survey on 22 October so the target of 10 was met and user testing will use 5 students and 1 lecturer</t>
+          <t>13 students answered the survey on 22 October so the target of 10 was met and the user testing on 28 October had 4 students and 2 lecturers</t>
         </is>
       </c>
     </row>
@@ -822,7 +830,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="K8" s="6" t="n">
@@ -830,7 +838,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Email service built and merged in Week 4 and reminders still to be tested</t>
+          <t>Confirmation and reminder tested in preview mode (TC-08a and TC-08b) and an SMTP test email was received on 23 October</t>
         </is>
       </c>
     </row>
@@ -880,7 +888,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="K9" s="6" t="n">
@@ -888,7 +896,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Unique key and role checks merged and access tests still to run</t>
+          <t>8 simultaneous requests gave one booking (TC-07) and other users records were refused in every access test (TC-14)</t>
         </is>
       </c>
     </row>
@@ -980,13 +988,17 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="K11" s="6" t="n">
         <v>46318</v>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Supervisor approved the survey and the user testing</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1209,12 +1221,12 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Planned for Week 4</t>
+          <t>Done in Week 4 (Chapter 5 Table 5.2 Test environment)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="K16" s="6" t="n">
